--- a/tracking_forms/037_helpline_status_check_form--tracking_forms.xlsx
+++ b/tracking_forms/037_helpline_status_check_form--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,9 +440,9 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>helpline_status_page</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>Is helpline active?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,35 +543,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>helpline_status</t>
+          <t>customer_support_page</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>helpline_status</t>
+          <t>Does customer support available?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>helpline_priority</t>
+          <t>issue_description_page</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>helpline_priority</t>
+          <t>Describe any issues</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>issue_description</t>
+          <t>priority_page</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>issue_description</t>
+          <t>Is priority set?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>customer_support</t>
+          <t>customer_support_status_page</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>customer_support</t>
+          <t>Is customer support active?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>customer_support_status</t>
+          <t>helpline_status_page_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>customer_support_status</t>
+          <t>Helpline Status</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>customer_support_priority</t>
+          <t>customer_support_page_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>customer_support_priority</t>
+          <t>Customer Support Page 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>customer_support_status</t>
+          <t>customer_support_status_page_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>customer_support_status</t>
+          <t>Customer Support Status Page 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>customer_support_priority</t>
+          <t>issue_description_page_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>customer_support_priority</t>
+          <t>Issue Description Page 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>customer_support_status</t>
+          <t>customer_note_page</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>customer_support_status</t>
+          <t>Any additional notes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -753,10 +753,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -781,7 +781,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>helpline_status_choices</t>
+          <t>helpline_status_page_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -798,7 +798,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>helpline_status_choices</t>
+          <t>helpline_status_page_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -815,75 +815,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>helpline_priority_choices</t>
+          <t>customer_support_page_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>helpline_priority_choices</t>
+          <t>customer_support_page_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>customer_support_choices</t>
+          <t>priority_page_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>customer_support_choices</t>
+          <t>priority_page_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>customer_support_status_choices</t>
+          <t>customer_support_status_page_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -900,7 +900,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>customer_support_status_choices</t>
+          <t>customer_support_status_page_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -917,134 +917,100 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>customer_support_priority_choices</t>
+          <t>helpline_status_page_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>customer_support_priority_choices</t>
+          <t>helpline_status_page_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>customer_support_status_choices</t>
+          <t>customer_support_page_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>customer_support_status_choices</t>
+          <t>customer_support_page_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>customer_support_priority_choices</t>
+          <t>customer_support_status_page_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>customer_support_priority_choices</t>
+          <t>customer_support_status_page_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>customer_support_status_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>customer_support_status_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
